--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 102 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 99 clubs short</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1940,8 +1940,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3028,8 +3028,8 @@
       <c r="P23" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Q23" s="9" t="n">
-        <v>1</v>
+      <c r="Q23" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>1</v>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="10" t="n">
         <v>1</v>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9077,8 +9077,8 @@
       <c r="T82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
+      <c r="U82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V82" s="9" t="n">
         <v>3</v>
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11350,8 +11350,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17939,13 +17939,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17986,8 +17986,8 @@
       <c r="V169" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W169" s="9" t="n">
-        <v>3</v>
+      <c r="W169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X169" s="10" t="n">
         <v>7</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -18321,7 +18321,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>4</v>
       </c>
       <c r="W173" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X173" s="10" t="n">
         <v>7</v>
@@ -18391,8 +18391,8 @@
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
@@ -19154,7 +19154,7 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q181" s="9" t="n">
         <v>1</v>
@@ -21788,7 +21788,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21854,7 +21854,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -22283,7 +22283,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -22877,7 +22877,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2862,7 +2866,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3064,7 +3072,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3165,7 +3177,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3367,7 +3383,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3569,7 +3589,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3981,7 +4005,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4393,7 +4421,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4595,7 +4627,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4696,7 +4732,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4898,7 +4938,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -6532,7 +6576,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6734,7 +6782,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6936,7 +6988,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8071,7 +8127,11 @@
       <c r="AB72" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -9101,7 +9161,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9719,7 +9783,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -10854,7 +10922,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -12179,7 +12251,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -13205,7 +13281,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13508,7 +13588,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -14019,7 +14103,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14120,7 +14208,11 @@
       <c r="AB131" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14423,7 +14515,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14524,7 +14620,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14625,7 +14725,11 @@
       <c r="AB136" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC136" s="4" t="inlineStr"/>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -15340,7 +15444,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -17083,7 +17191,11 @@
       <c r="AB160" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC160" s="4" t="inlineStr"/>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17386,7 +17498,11 @@
       <c r="AB163" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC163" s="4" t="inlineStr"/>
+      <c r="AC163" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 99 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 91 clubs short</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1330,8 +1330,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1738,8 +1738,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3051,11 +3051,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>2</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3063,8 +3063,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3568,11 +3568,11 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>2</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>7</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3658,8 +3658,8 @@
       <c r="P29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="9" t="n">
-        <v>1</v>
+      <c r="Q29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4929,8 +4929,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8946,8 +8946,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="U99" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V99" s="10" t="n">
         <v>4</v>
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12755,8 +12755,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13363,7 +13363,7 @@
         <v>1</v>
       </c>
       <c r="U123" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V123" s="9" t="n">
         <v>2</v>
@@ -13559,7 +13559,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="10" t="n">
         <v>1</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14187,11 +14187,11 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>3</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -16098,17 +16098,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -16143,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16665,8 +16665,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -16801,7 +16801,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16871,8 +16871,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17126,13 +17126,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -17170,11 +17170,11 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>3</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>7</v>
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>7</v>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
       <c r="P189" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q189" s="9" t="n">
         <v>0</v>
@@ -21209,7 +21209,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21267,8 +21267,8 @@
       <c r="U201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V201" s="9" t="n">
-        <v>1</v>
+      <c r="V201" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21421,13 +21421,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
@@ -21450,8 +21450,8 @@
       <c r="P203" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" s="9" t="n">
-        <v>0</v>
+      <c r="Q203" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R203" s="9" t="n">
         <v>0</v>
@@ -21469,7 +21469,7 @@
         <v>4</v>
       </c>
       <c r="W203" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X203" s="10" t="n">
         <v>7</v>
@@ -21605,7 +21605,7 @@
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21619,13 +21619,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L205" s="8" t="inlineStr">
         <is>
@@ -21663,8 +21663,8 @@
       <c r="U205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="9" t="n">
-        <v>0</v>
+      <c r="V205" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
@@ -21871,7 +21871,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21904,7 +21904,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21970,7 +21970,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -22003,7 +22003,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22036,7 +22036,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22102,7 +22102,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22366,7 +22366,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22630,7 +22630,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -22729,7 +22729,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22843,7 +22843,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -22861,7 +22861,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22894,7 +22894,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$207</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 91 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 58 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC206"/>
+  <dimension ref="A1:AC207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1217,11 +1217,11 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>1</v>
+      <c r="V5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1229,8 +1229,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2146,8 +2146,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2251,8 +2251,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2836,14 +2836,14 @@
       <c r="R21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="9" t="n">
-        <v>1</v>
+      <c r="S21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3034,16 +3034,16 @@
         </is>
       </c>
       <c r="P23" s="10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="9" t="n">
-        <v>0</v>
+      <c r="R23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="10" t="n">
         <v>2</v>
@@ -3670,8 +3670,8 @@
       <c r="T29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U29" s="9" t="n">
-        <v>0</v>
+      <c r="U29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3790,8 +3790,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>1</v>
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5339,8 +5339,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="9" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5541,8 +5541,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5949,8 +5949,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7084,8 +7084,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7466,8 +7466,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P66" s="9" t="n">
-        <v>2</v>
+      <c r="P66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7888,10 +7888,10 @@
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -7908,8 +7908,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8223,8 +8223,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8411,8 +8411,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8534,8 +8534,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8841,8 +8841,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9047,8 +9047,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9328,8 +9328,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P84" s="9" t="n">
-        <v>3</v>
+      <c r="P84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9508,13 +9508,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10172,8 +10172,8 @@
       <c r="S92" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -10501,8 +10501,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="9" t="n">
         <v>0</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10703,8 +10703,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11220,8 +11220,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11628,8 +11628,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11673,17 +11673,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
@@ -11721,7 +11721,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11729,8 +11729,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11830,8 +11830,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>1</v>
@@ -12475,15 +12475,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>4303877</v>
+        <v>28680931</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Professionals Toastmasters Club</t>
+          <t>Gulf O Flex Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12497,17 +12497,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -12524,10 +12524,10 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12542,26 +12542,24 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="10" t="n">
-        <v>7</v>
+      <c r="X115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="10" t="n">
-        <v>1</v>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB115" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AB115" s="4" t="n"/>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
@@ -12576,15 +12574,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28676820</v>
+        <v>4303877</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>The Propellors Club</t>
+          <t>Professionals Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12598,13 +12596,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12612,11 +12610,11 @@
         </is>
       </c>
       <c r="M116" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
@@ -12625,10 +12623,10 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12643,25 +12641,25 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
+      <c r="X116" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC116" s="4" t="inlineStr"/>
     </row>
@@ -12677,15 +12675,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>2257012</v>
+        <v>28676820</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>UAE Leaders Toastmasters Clubs</t>
+          <t>The Propellors Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12699,25 +12697,25 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O117" s="8" t="inlineStr">
@@ -12726,7 +12724,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12737,38 +12735,34 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W117" s="10" t="n">
-        <v>10</v>
+      <c r="V117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X117" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC117" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12782,15 +12776,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7726039</v>
+        <v>2257012</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Universal Toastmasters Club</t>
+          <t>UAE Leaders Toastmasters Clubs</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12804,17 +12798,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L118" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>14</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
@@ -12831,7 +12825,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
@@ -12842,20 +12836,20 @@
       <c r="S118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
+      <c r="V118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="X118" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12887,15 +12881,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>7830309</v>
+        <v>7726039</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>White Feathers Toastmasters Club</t>
+          <t>Universal Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12909,13 +12903,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -12945,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -12954,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12965,38 +12959,42 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>7806663</v>
+        <v>7830309</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Arabian Ranches Toastmasters Club</t>
+          <t>White Feathers Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13010,10 +13008,10 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>0</v>
@@ -13039,14 +13037,14 @@
       <c r="P120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" s="10" t="n">
-        <v>2</v>
+      <c r="Q120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="10" t="n">
         <v>1</v>
@@ -13073,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC120" s="4" t="inlineStr"/>
     </row>
@@ -13089,11 +13087,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>3922931</v>
+        <v>7806663</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>DIC2 Toastmasters Club</t>
+          <t>Arabian Ranches Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13111,17 +13109,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -13140,14 +13138,14 @@
       <c r="P121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T121" s="10" t="n">
         <v>1</v>
@@ -13155,11 +13153,11 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="10" t="n">
-        <v>4</v>
+      <c r="V121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -13174,13 +13172,9 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC121" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13194,15 +13188,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>624236</v>
+        <v>3922931</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Emirates Toastmasters Club</t>
+          <t>DIC2 Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13216,13 +13210,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13245,17 +13239,17 @@
       <c r="P122" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q122" s="9" t="n">
-        <v>1</v>
+      <c r="Q122" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
@@ -13264,7 +13258,7 @@
         <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>7</v>
@@ -13279,11 +13273,11 @@
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -13299,39 +13293,39 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>6938101</v>
+        <v>624236</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Media Masters Toastmasters Club</t>
+          <t>Emirates Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K123" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F123" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="J123" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K123" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -13348,25 +13342,25 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q123" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q123" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V123" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13384,9 +13378,13 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13400,15 +13398,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28676961</v>
+        <v>6938101</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Youth Global Program Toastmasters Club</t>
+          <t>Media Masters Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13422,13 +13420,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -13449,25 +13447,25 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q124" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13478,14 +13476,14 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC124" s="4" t="inlineStr"/>
     </row>
@@ -13497,19 +13495,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>2991308</v>
+        <v>28676961</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Discovery Gardens Toastmasters Club</t>
+          <t>Youth Global Program Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13523,17 +13521,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -13549,29 +13547,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P125" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q125" s="10" t="n">
-        <v>2</v>
+      <c r="P125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W125" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -13579,20 +13577,16 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC125" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13606,15 +13600,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7434848</v>
+        <v>2991308</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Dubai Tamil Malayalam Toastmasters Club</t>
+          <t>Discovery Gardens Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13628,13 +13622,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13654,11 +13648,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="9" t="n">
-        <v>0</v>
+      <c r="P126" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -13672,11 +13666,11 @@
       <c r="U126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W126" s="9" t="n">
-        <v>0</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W126" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>7</v>
@@ -13695,7 +13689,7 @@
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13711,15 +13705,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>6485446</v>
+        <v>7434848</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Greens Dubai Toastmaster Club</t>
+          <t>Dubai Tamil Malayalam Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13733,17 +13727,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13771,14 +13765,14 @@
       <c r="S127" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13796,11 +13790,11 @@
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC127" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -13816,15 +13810,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28679320</v>
+        <v>6485446</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Intertec Systems Toastmasters</t>
+          <t>Greens Dubai Toastmaster Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13838,13 +13832,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13874,7 +13868,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="9" t="n">
         <v>0</v>
@@ -13883,27 +13877,31 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13917,11 +13915,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28680914</v>
+        <v>28679320</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>McDermott Emirates Toastmasters Club</t>
+          <t>Intertec Systems Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13939,17 +13937,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
@@ -13984,13 +13982,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>0</v>
+      <c r="X129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14001,7 +13999,9 @@
       <c r="AA129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB129" s="4" t="n"/>
+      <c r="AB129" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AC129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
@@ -14016,15 +14016,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28675828</v>
+        <v>28680914</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>V4U Toastmasters Club</t>
+          <t>McDermott Emirates Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14038,13 +14038,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14082,14 +14082,14 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>0</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="X130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14100,14 +14100,8 @@
       <c r="AA130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB130" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC130" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB130" s="4" t="n"/>
+      <c r="AC130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14117,19 +14111,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7847812</v>
+        <v>28675828</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Ace It Marina Toastmasters Club</t>
+          <t>V4U Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14143,13 +14137,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14170,10 +14164,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -14187,11 +14181,11 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
+      <c r="V131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -14226,15 +14220,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>4809025</v>
+        <v>7847812</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>DIC Advanced</t>
+          <t>Ace It Marina Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14248,17 +14242,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L132" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -14275,10 +14269,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -14292,11 +14286,11 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>3</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>7</v>
@@ -14311,9 +14305,13 @@
         <v>1</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14327,11 +14325,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28678438</v>
+        <v>4809025</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>JITO Toastmasters</t>
+          <t>DIC Advanced</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -14349,13 +14347,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14394,13 +14392,13 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14412,7 +14410,7 @@
         <v>1</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC133" s="4" t="inlineStr"/>
     </row>
@@ -14428,15 +14426,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>5984189</v>
+        <v>28678438</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>JLT Dubai Toastmasters Club</t>
+          <t>JITO Toastmasters</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14450,17 +14448,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
@@ -14477,49 +14475,45 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Q134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W134" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X134" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB134" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC134" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14533,15 +14527,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>7783711</v>
+        <v>5984189</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>JVT Dubai Toastmasters Club</t>
+          <t>JLT Dubai Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14555,13 +14549,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14585,25 +14579,25 @@
         <v>3</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V135" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W135" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -14638,15 +14632,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28677185</v>
+        <v>7783711</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Luminous JLT Dubai Toastmasters Club</t>
+          <t>JVT Dubai Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14660,13 +14654,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14687,28 +14681,28 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V136" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>3</v>
+      <c r="W136" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -14739,19 +14733,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>4818768</v>
+        <v>28677185</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Luminous JLT Dubai Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14765,13 +14759,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14792,7 +14786,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14803,36 +14797,36 @@
       <c r="S137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="9" t="n">
-        <v>2</v>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC137" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -14848,15 +14842,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>7212928</v>
+        <v>4818768</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Cummins Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14870,17 +14864,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14915,27 +14909,31 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -14949,11 +14947,11 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28678712</v>
+        <v>7212928</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Gerab Toastmasters Club</t>
+          <t>Cummins Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -14971,17 +14969,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K139" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -15022,7 +15020,7 @@
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -15034,7 +15032,7 @@
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC139" s="4" t="inlineStr"/>
     </row>
@@ -15050,15 +15048,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>7988863</v>
+        <v>28678712</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>MES Brainstormers Toastmasters Club</t>
+          <t>Gerab Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15072,10 +15070,10 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>0</v>
@@ -15099,7 +15097,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
@@ -15128,20 +15126,16 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC140" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15155,15 +15149,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>7669950</v>
+        <v>7988863</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>St. Francis  Of Assisi Toastmasters Club</t>
+          <t>MES Brainstormers Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15177,13 +15171,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -15204,7 +15198,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -15215,17 +15209,17 @@
       <c r="S141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="10" t="n">
-        <v>4</v>
+      <c r="V141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>7</v>
@@ -15240,31 +15234,35 @@
         <v>1</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>28677655</v>
+        <v>7669950</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Barsha 2 Toastmasters Club</t>
+          <t>St. Francis  Of Assisi Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15278,17 +15276,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -15305,7 +15303,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -15316,32 +15314,32 @@
       <c r="S142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="9" t="n">
-        <v>0</v>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X142" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC142" s="4" t="inlineStr"/>
     </row>
@@ -15357,15 +15355,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>3589758</v>
+        <v>28677655</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Barsha Toastmasters Club</t>
+          <t>Barsha 2 Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15379,17 +15377,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -15415,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -15424,31 +15422,27 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="10" t="n">
-        <v>6</v>
+      <c r="X143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="10" t="n">
-        <v>1</v>
+      <c r="Z143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC143" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -15462,11 +15456,11 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28677250</v>
+        <v>3589758</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>CEKA Toastmasters</t>
+          <t>Barsha Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -15484,17 +15478,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M144" s="7" t="n">
@@ -15522,36 +15516,36 @@
       <c r="S144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC144" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -15567,15 +15561,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1989858</v>
+        <v>28677250</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>HSBC Corporate Toastmasters Club</t>
+          <t>CEKA Toastmasters</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15589,10 +15583,10 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K145" s="4" t="n">
         <v>0</v>
@@ -15603,11 +15597,11 @@
         </is>
       </c>
       <c r="M145" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O145" s="8" t="inlineStr">
@@ -15625,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -15639,22 +15633,26 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>0</v>
+      <c r="X145" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC145" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -15668,15 +15666,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>2913</v>
+        <v>1989858</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Star of Arabia Club</t>
+          <t>HSBC Corporate Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15690,25 +15688,25 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
@@ -15728,8 +15726,8 @@
       <c r="S146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="10" t="n">
-        <v>1</v>
+      <c r="T146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U146" s="9" t="n">
         <v>0</v>
@@ -15740,26 +15738,22 @@
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="10" t="n">
-        <v>7</v>
+      <c r="X146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA146" s="10" t="n">
-        <v>1</v>
+      <c r="Z146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC146" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -15773,15 +15767,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28679238</v>
+        <v>2913</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Transworld Toastmasters Club</t>
+          <t>Star of Arabia Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15795,25 +15789,25 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L147" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M147" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O147" s="8" t="inlineStr">
@@ -15833,8 +15827,8 @@
       <c r="S147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U147" s="9" t="n">
         <v>0</v>
@@ -15845,22 +15839,26 @@
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
+      <c r="X147" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC147" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -15870,15 +15868,15 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>2532218</v>
+        <v>28679238</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Business Excellence Toastmasters Club</t>
+          <t>Transworld Toastmasters Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15959,7 +15957,7 @@
         <v>0</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC148" s="4" t="inlineStr"/>
     </row>
@@ -15975,11 +15973,11 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>652941</v>
+        <v>2532218</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Creek Club</t>
+          <t>Business Excellence Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -15997,10 +15995,10 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>0</v>
@@ -16011,11 +16009,11 @@
         </is>
       </c>
       <c r="M149" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O149" s="8" t="inlineStr">
@@ -16024,7 +16022,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -16047,8 +16045,8 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="10" t="n">
-        <v>7</v>
+      <c r="X149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -16056,11 +16054,11 @@
       <c r="Z149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA149" s="10" t="n">
-        <v>1</v>
+      <c r="AA149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC149" s="4" t="inlineStr"/>
     </row>
@@ -16076,11 +16074,11 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>7158853</v>
+        <v>652941</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Dubai Arabic Toastmasters Club</t>
+          <t>Creek Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -16098,17 +16096,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -16125,7 +16123,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
@@ -16133,8 +16131,8 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="10" t="n">
-        <v>2</v>
+      <c r="S150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -16143,25 +16141,25 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X150" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB150" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB150" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="AC150" s="4" t="inlineStr"/>
     </row>
@@ -16177,15 +16175,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>7856650</v>
+        <v>7158853</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>IIEE &amp; Friends Toastmaster Club</t>
+          <t>Dubai Arabic Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16199,17 +16197,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16226,43 +16224,43 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="10" t="n">
-        <v>1</v>
+      <c r="S151" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC151" s="4" t="inlineStr"/>
     </row>
@@ -16278,15 +16276,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>28680761</v>
+        <v>7856650</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Leaders’ Voice Toastmasters Club</t>
+          <t>IIEE &amp; Friends Toastmaster Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16300,17 +16298,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="7" t="n">
@@ -16330,7 +16328,7 @@
         <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
@@ -16338,14 +16336,14 @@
       <c r="S152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T152" s="9" t="n">
-        <v>0</v>
+      <c r="T152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16362,7 +16360,9 @@
       <c r="AA152" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB152" s="4" t="n"/>
+      <c r="AB152" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="AC152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
@@ -16377,15 +16377,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>2254635</v>
+        <v>28680761</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>TRISTAR Toastmasters Club</t>
+          <t>Leaders’ Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
         <v>2</v>
@@ -16455,20 +16455,14 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="10" t="n">
-        <v>1</v>
+      <c r="Z153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB153" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC153" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB153" s="4" t="n"/>
+      <c r="AC153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16478,19 +16472,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1670793</v>
+        <v>2254635</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Digerati Toastmasters Club</t>
+          <t>TRISTAR Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16504,17 +16498,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -16549,7 +16543,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16560,8 +16554,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -16587,15 +16581,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>919010</v>
+        <v>1670793</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Dunes Toastmasters Club</t>
+          <t>Digerati Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16609,17 +16603,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
@@ -16654,19 +16648,19 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X155" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="10" t="n">
-        <v>1</v>
+      <c r="Z155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -16674,7 +16668,11 @@
       <c r="AB155" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -16688,15 +16686,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>28677800</v>
+        <v>919010</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>International Elite Speakers Toastmasters Club</t>
+          <t>Dunes Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16713,10 +16711,10 @@
         <v>20</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16755,31 +16753,27 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC156" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -16793,15 +16787,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1055870</v>
+        <v>28677800</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>International Elite Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16815,13 +16809,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16842,7 +16836,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -16859,11 +16853,11 @@
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="10" t="n">
-        <v>4</v>
+      <c r="V157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>7</v>
@@ -16871,18 +16865,18 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="10" t="n">
-        <v>1</v>
+      <c r="Z157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB157" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC157" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -16898,15 +16892,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>5409350</v>
+        <v>1055870</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Voltas International Toastmasters Club</t>
+          <t>SLP</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16920,13 +16914,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -16947,7 +16941,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16958,17 +16952,17 @@
       <c r="S158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T158" s="9" t="n">
-        <v>0</v>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="9" t="n">
-        <v>0</v>
+      <c r="V158" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>7</v>
@@ -16976,16 +16970,20 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB158" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC158" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -16995,19 +16993,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>2741533</v>
+        <v>5409350</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Bowlers Toastmasters Club</t>
+          <t>Voltas International Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17021,17 +17019,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L159" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M159" s="7" t="n">
@@ -17077,20 +17075,16 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB159" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC159" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17104,15 +17098,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>3373392</v>
+        <v>2741533</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Desert Divas</t>
+          <t>Bowlers Toastmasters Club</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17126,17 +17120,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -17164,17 +17158,17 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="10" t="n">
-        <v>1</v>
+      <c r="T160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="10" t="n">
-        <v>4</v>
+      <c r="V160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>7</v>
@@ -17189,11 +17183,11 @@
         <v>1</v>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -17209,11 +17203,11 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>909218</v>
+        <v>3373392</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Dubai Internet City Toastmasters Club</t>
+          <t>Desert Divas</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -17231,13 +17225,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17245,11 +17239,11 @@
         </is>
       </c>
       <c r="M161" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N161" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O161" s="8" t="inlineStr">
@@ -17258,16 +17252,16 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S161" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T161" s="10" t="n">
         <v>1</v>
@@ -17278,8 +17272,8 @@
       <c r="V161" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W161" s="10" t="n">
-        <v>4</v>
+      <c r="W161" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>7</v>
@@ -17290,13 +17284,17 @@
       <c r="Z161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA161" s="9" t="n">
-        <v>0</v>
+      <c r="AA161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB161" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC161" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC161" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -17310,11 +17308,11 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>28678518</v>
+        <v>909218</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Paramount Toastmasters Club</t>
+          <t>Dubai Internet City Toastmasters Club</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -17332,13 +17330,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17346,11 +17344,11 @@
         </is>
       </c>
       <c r="M162" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N162" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O162" s="8" t="inlineStr">
@@ -17362,16 +17360,16 @@
         <v>0</v>
       </c>
       <c r="Q162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U162" s="9" t="n">
         <v>0</v>
@@ -17380,7 +17378,7 @@
         <v>4</v>
       </c>
       <c r="W162" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>7</v>
@@ -17391,8 +17389,8 @@
       <c r="Z162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA162" s="10" t="n">
-        <v>1</v>
+      <c r="AA162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB162" s="4" t="n">
         <v>3</v>
@@ -17411,15 +17409,15 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>833229</v>
+        <v>28678518</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>UAE Advanced Toastmasters Club</t>
+          <t>Paramount Toastmasters Club</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17433,13 +17431,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -17460,7 +17458,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -17480,8 +17478,8 @@
       <c r="V163" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W163" s="9" t="n">
-        <v>1</v>
+      <c r="W163" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>7</v>
@@ -17496,13 +17494,9 @@
         <v>1</v>
       </c>
       <c r="AB163" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC163" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -17512,15 +17506,15 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>28679555</v>
+        <v>833229</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Al Ghurair Toastmasters Club</t>
+          <t>UAE Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -17538,13 +17532,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -17565,7 +17559,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -17586,7 +17580,7 @@
         <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>7</v>
@@ -17601,9 +17595,13 @@
         <v>1</v>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC164" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -17617,15 +17615,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>7791917</v>
+        <v>28679555</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Dubai Legends Toastmasters Club</t>
+          <t>Al Ghurair Toastmasters Club</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17639,13 +17637,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17683,11 +17681,11 @@
       <c r="U165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="9" t="n">
-        <v>0</v>
+      <c r="V165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>7</v>
@@ -17695,20 +17693,16 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB165" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC165" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -17722,15 +17716,15 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>28676939</v>
+        <v>7791917</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Flydubai Toastmaster Club</t>
+          <t>Dubai Legends Toastmasters Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17744,25 +17738,25 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L166" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M166" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O166" s="8" t="inlineStr">
@@ -17794,22 +17788,26 @@
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="9" t="n">
-        <v>0</v>
+      <c r="X166" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -17823,15 +17821,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>28675380</v>
+        <v>28676939</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>LEAMS Toastmasters Club</t>
+          <t>Flydubai Toastmaster Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17845,25 +17843,25 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O167" s="8" t="inlineStr">
@@ -17872,7 +17870,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -17890,31 +17888,27 @@
         <v>0</v>
       </c>
       <c r="V167" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X167" s="10" t="n">
-        <v>7</v>
+      <c r="X167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA167" s="10" t="n">
-        <v>1</v>
+      <c r="Z167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB167" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC167" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -17928,15 +17922,15 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>28677399</v>
+        <v>28675380</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>WASL VILLAGE TOASTMASTERS CLUB</t>
+          <t>LEAMS Toastmasters Club</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17950,13 +17944,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -17977,25 +17971,25 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q168" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R168" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="10" t="n">
-        <v>1</v>
+      <c r="T168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -18013,7 +18007,7 @@
         <v>1</v>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -18024,20 +18018,20 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>748095</v>
+        <v>28677399</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Abjad Toastmasters Club</t>
+          <t>WASL VILLAGE TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -18055,13 +18049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18084,26 +18078,26 @@
       <c r="P169" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q169" s="9" t="n">
-        <v>1</v>
+      <c r="Q169" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S169" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T169" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V169" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W169" s="10" t="n">
-        <v>4</v>
+      <c r="V169" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X169" s="10" t="n">
         <v>7</v>
@@ -18117,8 +18111,14 @@
       <c r="AA169" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB169" s="4" t="n"/>
-      <c r="AC169" s="4" t="inlineStr"/>
+      <c r="AB169" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -18132,15 +18132,15 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>976090</v>
+        <v>748095</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Spectrum Toastmasters</t>
+          <t>Abjad Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -18154,17 +18154,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M170" s="7" t="n">
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R170" s="9" t="n">
         <v>0</v>
@@ -18192,17 +18192,17 @@
       <c r="S170" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T170" s="10" t="n">
-        <v>1</v>
+      <c r="T170" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V170" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W170" s="9" t="n">
-        <v>0</v>
+      <c r="V170" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W170" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X170" s="10" t="n">
         <v>7</v>
@@ -18231,15 +18231,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1950</v>
+        <v>976090</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Toastmasters</t>
+          <t>Abu Dhabi Spectrum Toastmasters</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18253,17 +18253,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L171" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="7" t="n">
@@ -18279,11 +18279,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P171" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q171" s="10" t="n">
-        <v>2</v>
+      <c r="P171" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q171" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18294,14 +18294,14 @@
       <c r="T171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U171" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V171" s="10" t="n">
-        <v>4</v>
+      <c r="U171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>7</v>
@@ -18330,15 +18330,15 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>28676397</v>
+        <v>1950</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Worley UAE</t>
+          <t>Abu Dhabi Toastmasters</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18352,25 +18352,25 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M172" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O172" s="8" t="inlineStr">
@@ -18378,41 +18378,41 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q172" s="9" t="n">
-        <v>0</v>
+      <c r="P172" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q172" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X172" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB172" s="4" t="n"/>
       <c r="AC172" s="4" t="inlineStr"/>
@@ -18425,19 +18425,19 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>882137</v>
+        <v>28676397</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Intilaaqah Abu Dhabi Club</t>
+          <t>Worley UAE</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18451,25 +18451,25 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L173" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M173" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O173" s="8" t="inlineStr">
@@ -18495,23 +18495,23 @@
       <c r="U173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V173" s="10" t="n">
-        <v>4</v>
+      <c r="V173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W173" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X173" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA173" s="10" t="n">
-        <v>1</v>
+      <c r="Z173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB173" s="4" t="n"/>
       <c r="AC173" s="4" t="inlineStr"/>
@@ -18528,15 +18528,15 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>6655446</v>
+        <v>882137</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Khalifa City Toastmasters</t>
+          <t>Intilaaqah Abu Dhabi Club</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18550,13 +18550,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18576,8 +18576,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P174" s="10" t="n">
-        <v>4</v>
+      <c r="P174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q174" s="9" t="n">
         <v>0</v>
@@ -18588,17 +18588,17 @@
       <c r="S174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T174" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U174" s="10" t="n">
-        <v>1</v>
+      <c r="T174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V174" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W174" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X174" s="10" t="n">
         <v>7</v>
@@ -18627,15 +18627,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28676568</v>
+        <v>6655446</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Majd</t>
+          <t>Khalifa City Toastmasters</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18649,17 +18649,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L175" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M175" s="7" t="n">
@@ -18675,8 +18675,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P175" s="9" t="n">
-        <v>0</v>
+      <c r="P175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>0</v>
@@ -18687,17 +18687,17 @@
       <c r="S175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V175" s="9" t="n">
-        <v>3</v>
+      <c r="T175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>7</v>
@@ -18726,15 +18726,15 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>28679349</v>
+        <v>28676568</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Zayed University</t>
+          <t>Majd</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18748,13 +18748,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
@@ -18762,11 +18762,11 @@
         </is>
       </c>
       <c r="M176" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O176" s="8" t="inlineStr">
@@ -18793,7 +18793,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -18804,11 +18804,11 @@
       <c r="Y176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA176" s="9" t="n">
-        <v>0</v>
+      <c r="Z176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB176" s="4" t="n"/>
       <c r="AC176" s="4" t="inlineStr"/>
@@ -18821,19 +18821,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>2044089</v>
+        <v>28679349</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Humoroids Toastmasters Club</t>
+          <t>Zayed University</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18847,25 +18847,25 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M177" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O177" s="8" t="inlineStr">
@@ -18874,10 +18874,10 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q177" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
@@ -18892,7 +18892,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -18903,11 +18903,11 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA177" s="10" t="n">
-        <v>1</v>
+      <c r="Z177" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA177" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB177" s="4" t="n"/>
       <c r="AC177" s="4" t="inlineStr"/>
@@ -18924,15 +18924,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>28679331</v>
+        <v>2044089</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>MBZUAI</t>
+          <t>Humoroids Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18946,25 +18946,25 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M178" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
@@ -18973,10 +18973,10 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R178" s="9" t="n">
         <v>0</v>
@@ -18991,22 +18991,22 @@
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="9" t="n">
-        <v>0</v>
+      <c r="X178" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA178" s="9" t="n">
-        <v>0</v>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB178" s="4" t="n"/>
       <c r="AC178" s="4" t="inlineStr"/>
@@ -19023,15 +19023,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>6664</v>
+        <v>28679331</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Millennium Toastmasters Club</t>
+          <t>MBZUAI</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19045,25 +19045,25 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O179" s="8" t="inlineStr">
@@ -19081,7 +19081,7 @@
         <v>0</v>
       </c>
       <c r="S179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" s="9" t="n">
         <v>0</v>
@@ -19090,22 +19090,22 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X179" s="10" t="n">
-        <v>7</v>
+      <c r="X179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA179" s="10" t="n">
-        <v>1</v>
+      <c r="Z179" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB179" s="4" t="n"/>
       <c r="AC179" s="4" t="inlineStr"/>
@@ -19122,15 +19122,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1901915</v>
+        <v>6664</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Mussafah Toastmasters</t>
+          <t>Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19144,13 +19144,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -19170,29 +19170,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P180" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q180" s="10" t="n">
+      <c r="P180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W180" s="10" t="n">
-        <v>6</v>
+      <c r="W180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X180" s="10" t="n">
         <v>7</v>
@@ -19221,15 +19221,15 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>4544070</v>
+        <v>1901915</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>The Hive Toastmaster Club</t>
+          <t>Mussafah Toastmasters</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19243,13 +19243,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19269,17 +19269,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P181" s="9" t="n">
+      <c r="P181" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q181" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S181" s="9" t="n">
-        <v>0</v>
+      <c r="S181" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T181" s="9" t="n">
         <v>0</v>
@@ -19287,11 +19287,11 @@
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W181" s="9" t="n">
-        <v>0</v>
+      <c r="V181" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W181" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>7</v>
@@ -19316,39 +19316,39 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>28678947</v>
+        <v>4544070</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Orators</t>
+          <t>The Hive Toastmaster Club</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K182" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F182" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G182" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="J182" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K182" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q182" s="9" t="n">
         <v>1</v>
@@ -19380,14 +19380,14 @@
       <c r="S182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T182" s="10" t="n">
-        <v>1</v>
+      <c r="T182" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19419,15 +19419,15 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>28680794</v>
+        <v>28678947</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>CG Toastmasters Club</t>
+          <t>Abu Dhabi Orators</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19441,13 +19441,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19468,10 +19468,10 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
@@ -19479,26 +19479,26 @@
       <c r="S183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T183" s="9" t="n">
-        <v>0</v>
+      <c r="T183" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U183" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V183" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X183" s="9" t="n">
-        <v>0</v>
+      <c r="X183" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z183" s="9" t="n">
-        <v>0</v>
+      <c r="Z183" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA183" s="10" t="n">
         <v>1</v>
@@ -19518,15 +19518,15 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>7831529</v>
+        <v>28680794</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>CMA Toastmasters Club - UAE</t>
+          <t>CG Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19540,17 +19540,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L184" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M184" s="7" t="n">
@@ -19585,19 +19585,19 @@
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="10" t="n">
-        <v>7</v>
+      <c r="X184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="10" t="n">
-        <v>1</v>
+      <c r="Z184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA184" s="10" t="n">
         <v>1</v>
@@ -19617,15 +19617,15 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>28677253</v>
+        <v>7831529</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>KelvinTalks Toastmasters Club</t>
+          <t>CMA Toastmasters Club - UAE</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19639,17 +19639,17 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K185" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L185" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L185" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M185" s="7" t="n">
@@ -19695,8 +19695,8 @@
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -19716,15 +19716,15 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>28679393</v>
+        <v>28677253</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>SCAD Toastmasters Club</t>
+          <t>KelvinTalks Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19738,25 +19738,25 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M186" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N186" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O186" s="8" t="inlineStr">
@@ -19783,22 +19783,22 @@
         <v>0</v>
       </c>
       <c r="V186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="9" t="n">
-        <v>0</v>
+      <c r="X186" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA186" s="9" t="n">
-        <v>0</v>
+      <c r="Z186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA186" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB186" s="4" t="n"/>
       <c r="AC186" s="4" t="inlineStr"/>
@@ -19815,11 +19815,11 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>7683381</v>
+        <v>28679393</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Tech Talk Leaders Toastmasters Club</t>
+          <t>SCAD Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
@@ -19837,10 +19837,10 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K187" s="4" t="n">
         <v>0</v>
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="P187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q187" s="9" t="n">
         <v>0</v>
@@ -19887,8 +19887,8 @@
       <c r="W187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X187" s="10" t="n">
-        <v>7</v>
+      <c r="X187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
@@ -19905,24 +19905,24 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>606239</v>
+        <v>7683381</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Basharia Toastmasters Club</t>
+          <t>Tech Talk Leaders Toastmasters Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19936,13 +19936,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L188" s="8" t="inlineStr">
         <is>
@@ -19950,11 +19950,11 @@
         </is>
       </c>
       <c r="M188" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N188" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O188" s="8" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="P188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q188" s="9" t="n">
         <v>0</v>
@@ -19974,14 +19974,14 @@
       <c r="S188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T188" s="10" t="n">
-        <v>1</v>
+      <c r="T188" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U188" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V188" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -19995,8 +19995,8 @@
       <c r="Z188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA188" s="10" t="n">
-        <v>1</v>
+      <c r="AA188" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB188" s="4" t="n"/>
       <c r="AC188" s="4" t="inlineStr"/>
@@ -20013,15 +20013,15 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>1334189</v>
+        <v>606239</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>ISC Toastmasters Club</t>
+          <t>Basharia Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -20035,17 +20035,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L189" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M189" s="7" t="n">
@@ -20062,25 +20062,25 @@
         </is>
       </c>
       <c r="P189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="Q189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V189" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
@@ -20112,15 +20112,15 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>28679265</v>
+        <v>1334189</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>PICPA ABU DHABI Toastmasters Club</t>
+          <t>ISC Toastmasters Club</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -20134,13 +20134,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="P190" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q190" s="9" t="n">
         <v>0</v>
@@ -20179,7 +20179,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20190,8 +20190,8 @@
       <c r="Y190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z190" s="9" t="n">
-        <v>0</v>
+      <c r="Z190" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA190" s="10" t="n">
         <v>1</v>
@@ -20211,15 +20211,15 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>7852171</v>
+        <v>28679265</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>PSME Abu Dhabi &amp; Friends Toastmaster Club</t>
+          <t>PICPA ABU DHABI Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20233,13 +20233,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q191" s="9" t="n">
         <v>0</v>
@@ -20271,14 +20271,14 @@
       <c r="S191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T191" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U191" s="10" t="n">
-        <v>3</v>
+      <c r="T191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20310,15 +20310,15 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>7661403</v>
+        <v>7852171</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>The Professionals Toastmasters Club</t>
+          <t>PSME Abu Dhabi &amp; Friends Toastmaster Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20332,10 +20332,10 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>2</v>
@@ -20358,8 +20358,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P192" s="10" t="n">
-        <v>4</v>
+      <c r="P192" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q192" s="9" t="n">
         <v>0</v>
@@ -20368,13 +20368,13 @@
         <v>0</v>
       </c>
       <c r="S192" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T192" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U192" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V192" s="9" t="n">
         <v>2</v>
@@ -20405,19 +20405,19 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>28675407</v>
+        <v>7661403</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Malayalam Toastmasters Club</t>
+          <t>The Professionals Toastmasters Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20431,17 +20431,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M193" s="7" t="n">
@@ -20457,8 +20457,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P193" s="9" t="n">
-        <v>0</v>
+      <c r="P193" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q193" s="9" t="n">
         <v>0</v>
@@ -20467,16 +20467,16 @@
         <v>0</v>
       </c>
       <c r="S193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U193" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V193" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W193" s="9" t="n">
         <v>0</v>
@@ -20508,15 +20508,15 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>930087</v>
+        <v>28675407</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Speakers Bureau Toastmasters Club</t>
+          <t>Abu Dhabi Malayalam Toastmasters Club</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20530,10 +20530,10 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K194" s="4" t="n">
         <v>0</v>
@@ -20586,8 +20586,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -20607,15 +20607,15 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>584495</v>
+        <v>930087</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Al Ain Toastmasters Club</t>
+          <t>Abu Dhabi Speakers Bureau Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20629,17 +20629,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L195" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L195" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M195" s="7" t="n">
@@ -20656,16 +20656,16 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q195" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R195" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S195" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T195" s="9" t="n">
         <v>0</v>
@@ -20673,11 +20673,11 @@
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W195" s="10" t="n">
-        <v>4</v>
+      <c r="V195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X195" s="10" t="n">
         <v>7</v>
@@ -20685,8 +20685,8 @@
       <c r="Y195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z195" s="10" t="n">
-        <v>1</v>
+      <c r="Z195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA195" s="10" t="n">
         <v>1</v>
@@ -20706,15 +20706,15 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>28680521</v>
+        <v>584495</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>GENDER BALANCE Toastmasters</t>
+          <t>Al Ain Toastmasters Club</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20728,13 +20728,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
@@ -20755,16 +20755,16 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R196" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T196" s="9" t="n">
         <v>0</v>
@@ -20772,20 +20772,20 @@
       <c r="U196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W196" s="9" t="n">
-        <v>0</v>
+      <c r="V196" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W196" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X196" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z196" s="9" t="n">
-        <v>0</v>
+      <c r="Z196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA196" s="10" t="n">
         <v>1</v>
@@ -20805,15 +20805,15 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>6895468</v>
+        <v>28680521</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>TKM Toastmasters Club</t>
+          <t>GENDER BALANCE Toastmasters</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -20827,17 +20827,17 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M197" s="7" t="n">
@@ -20872,19 +20872,19 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X197" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z197" s="10" t="n">
-        <v>1</v>
+      <c r="Z197" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA197" s="10" t="n">
         <v>1</v>
@@ -20900,19 +20900,19 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>7906241</v>
+        <v>6895468</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Al Ruwais Toastmasters Club</t>
+          <t>TKM Toastmasters Club</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -20926,13 +20926,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" s="8" t="inlineStr">
         <is>
@@ -20971,19 +20971,19 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X198" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z198" s="9" t="n">
-        <v>0</v>
+      <c r="Z198" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA198" s="10" t="n">
         <v>1</v>
@@ -21003,15 +21003,15 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>28676936</v>
+        <v>7906241</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>IIEE Abu Dhabi and Friends Toastmasters Club</t>
+          <t>Al Ruwais Toastmasters Club</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -21025,10 +21025,10 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J199" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K199" s="4" t="n">
         <v>0</v>
@@ -21039,11 +21039,11 @@
         </is>
       </c>
       <c r="M199" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N199" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O199" s="8" t="inlineStr">
@@ -21055,7 +21055,7 @@
         <v>0</v>
       </c>
       <c r="Q199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" s="9" t="n">
         <v>0</v>
@@ -21075,17 +21075,17 @@
       <c r="W199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X199" s="9" t="n">
-        <v>1</v>
+      <c r="X199" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z199" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA199" s="9" t="n">
-        <v>0</v>
+      <c r="Z199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB199" s="4" t="n"/>
       <c r="AC199" s="4" t="inlineStr"/>
@@ -21102,15 +21102,15 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>925620</v>
+        <v>28676936</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Inner Universe Toastmasters Club</t>
+          <t>IIEE Abu Dhabi and Friends Toastmasters Club</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -21124,25 +21124,25 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L200" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N200" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O200" s="8" t="inlineStr">
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="P200" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q200" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" s="9" t="n">
         <v>0</v>
@@ -21169,22 +21169,22 @@
         <v>0</v>
       </c>
       <c r="V200" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X200" s="10" t="n">
-        <v>7</v>
+      <c r="X200" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z200" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA200" s="10" t="n">
-        <v>1</v>
+      <c r="Z200" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB200" s="4" t="n"/>
       <c r="AC200" s="4" t="inlineStr"/>
@@ -21201,15 +21201,15 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>7637212</v>
+        <v>925620</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>PICE-UAE &amp; Fellows Toastmasters Club</t>
+          <t>Inner Universe Toastmasters Club</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J201" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21261,8 +21261,8 @@
       <c r="S201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="10" t="n">
-        <v>1</v>
+      <c r="T201" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U201" s="9" t="n">
         <v>0</v>
@@ -21271,7 +21271,7 @@
         <v>4</v>
       </c>
       <c r="W201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X201" s="10" t="n">
         <v>7</v>
@@ -21296,19 +21296,19 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>7286067</v>
+        <v>7637212</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Knights (ADK) Toastmasters</t>
+          <t>PICE-UAE &amp; Fellows Toastmasters Club</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -21322,13 +21322,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21349,28 +21349,28 @@
         </is>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q202" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R202" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S202" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V202" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V202" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W202" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X202" s="10" t="n">
         <v>7</v>
@@ -21399,15 +21399,15 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>788926</v>
+        <v>7286067</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Women's Toastmasters Club</t>
+          <t>Abu Dhabi Knights (ADK) Toastmasters</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21421,10 +21421,10 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K203" s="4" t="n">
         <v>5</v>
@@ -21448,16 +21448,16 @@
         </is>
       </c>
       <c r="P203" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q203" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q203" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R203" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S203" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T203" s="9" t="n">
         <v>0</v>
@@ -21498,15 +21498,15 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>28680519</v>
+        <v>788926</v>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>ADNOC Drilling Toastmasters Club</t>
+          <t>Abu Dhabi Women's Toastmasters Club</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -21520,13 +21520,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
@@ -21547,10 +21547,10 @@
         </is>
       </c>
       <c r="P204" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q204" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R204" s="9" t="n">
         <v>0</v>
@@ -21564,11 +21564,11 @@
       <c r="U204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="9" t="n">
-        <v>0</v>
+      <c r="V204" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W204" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X204" s="10" t="n">
         <v>7</v>
@@ -21576,8 +21576,8 @@
       <c r="Y204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z204" s="9" t="n">
-        <v>0</v>
+      <c r="Z204" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA204" s="10" t="n">
         <v>1</v>
@@ -21597,15 +21597,15 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>28678774</v>
+        <v>28680519</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Fits UAE &amp; Friends Achievers Toastmasters Club</t>
+          <t>ADNOC Drilling Toastmasters Club</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21619,25 +21619,25 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J205" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L205" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M205" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O205" s="8" t="inlineStr">
@@ -21663,8 +21663,8 @@
       <c r="U205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="10" t="n">
-        <v>4</v>
+      <c r="V205" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
@@ -21678,8 +21678,8 @@
       <c r="Z205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA205" s="9" t="n">
-        <v>0</v>
+      <c r="AA205" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB205" s="4" t="n"/>
       <c r="AC205" s="4" t="inlineStr"/>
@@ -21696,15 +21696,15 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>4066</v>
+        <v>28678774</v>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>NMC Corporate Chapter Club</t>
+          <t>Fits UAE &amp; Friends Achievers Toastmasters Club</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F206" s="6" t="n">
         <v>10</v>
@@ -21718,25 +21718,25 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J206" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L206" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M206" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O206" s="8" t="inlineStr">
@@ -21756,14 +21756,14 @@
       <c r="S206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T206" s="10" t="n">
-        <v>1</v>
+      <c r="T206" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V206" s="9" t="n">
-        <v>0</v>
+      <c r="V206" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W206" s="9" t="n">
         <v>0</v>
@@ -21774,17 +21774,116 @@
       <c r="Y206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z206" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA206" s="10" t="n">
-        <v>1</v>
+      <c r="Z206" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB206" s="4" t="n"/>
       <c r="AC206" s="4" t="inlineStr"/>
     </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>4066</v>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>NMC Corporate Chapter Club</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F207" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G207" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J207" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O207" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X207" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB207" s="4" t="n"/>
+      <c r="AC207" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC206"/>
+  <autoFilter ref="A1:AC207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21871,7 +21970,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21886,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -21937,7 +22036,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21970,13 +22069,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22036,7 +22135,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22135,7 +22234,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22168,7 +22267,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -22267,7 +22366,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22300,7 +22399,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22333,7 +22432,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -22366,7 +22465,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22399,7 +22498,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22465,7 +22564,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -22498,7 +22597,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22531,7 +22630,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -22564,7 +22663,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22579,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -22627,16 +22726,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -22645,7 +22744,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -22663,7 +22762,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22696,7 +22795,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22729,13 +22828,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -22762,7 +22861,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22795,7 +22894,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22828,7 +22927,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22861,7 +22960,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22894,7 +22993,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22927,7 +23026,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -23059,7 +23158,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -23092,7 +23191,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -23158,7 +23257,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -23191,7 +23290,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2134,8 +2134,8 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23" s="10" t="n">
         <v>5</v>
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3359,8 +3359,8 @@
       <c r="T26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U26" s="9" t="n">
-        <v>0</v>
+      <c r="U26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
         <v>4</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3565,14 +3565,14 @@
       <c r="T28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U28" s="9" t="n">
-        <v>0</v>
+      <c r="U28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>1</v>
+      <c r="W28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>7</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3673,11 +3673,11 @@
       <c r="U29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>0</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3685,8 +3685,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3882,8 +3882,8 @@
       <c r="V31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>2</v>
+      <c r="W31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3987,8 +3987,8 @@
       <c r="V32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>3</v>
+      <c r="W32" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>1</v>
@@ -4086,14 +4086,14 @@
       <c r="T33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
+      <c r="U33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>1</v>
+      <c r="W33" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>7</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4356,13 +4356,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4711,11 +4711,11 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>3</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4873,17 +4873,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5077,17 +5077,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="10" t="n">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5327,11 +5327,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>1</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5530,7 +5530,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5586,17 +5586,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5627,8 +5627,8 @@
       <c r="T48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U48" s="9" t="n">
-        <v>0</v>
+      <c r="U48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V48" s="9" t="n">
         <v>2</v>
@@ -5691,13 +5691,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5792,17 +5792,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5840,7 +5840,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5937,11 +5937,11 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="9" t="n">
-        <v>0</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W51" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>7</v>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6143,11 +6143,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>1</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>7</v>
@@ -6204,13 +6204,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6406,13 +6406,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6511,17 +6511,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
@@ -6717,13 +6717,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6952,8 +6952,8 @@
       <c r="P61" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" s="9" t="n">
-        <v>0</v>
+      <c r="Q61" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -6965,13 +6965,13 @@
         <v>1</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>3</v>
+      <c r="W61" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7028,13 +7028,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7072,11 +7072,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7133,17 +7133,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7440,13 +7440,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7484,11 +7484,11 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>1</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7957,17 +7957,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8106,11 +8106,11 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="9" t="n">
-        <v>1</v>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8268,13 +8268,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8583,13 +8583,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8684,13 +8684,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8785,17 +8785,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="7" t="n">
@@ -8833,7 +8833,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8934,11 +8934,11 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>1</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>6</v>
@@ -8991,17 +8991,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="7" t="n">
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9096,13 +9096,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9140,11 +9140,11 @@
       <c r="U82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W82" s="9" t="n">
-        <v>0</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W82" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>7</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9302,13 +9302,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9331,8 +9331,8 @@
       <c r="P84" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" s="9" t="n">
-        <v>0</v>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -9407,13 +9407,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -9508,13 +9508,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9613,13 +9613,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9718,13 +9718,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9928,17 +9928,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -10134,17 +10134,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="7" t="n">
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>7</v>
@@ -10445,13 +10445,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10546,13 +10546,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10752,13 +10752,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>7</v>
@@ -11063,13 +11063,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11164,13 +11164,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11265,13 +11265,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
@@ -11366,17 +11366,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="7" t="n">
@@ -11471,13 +11471,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -11572,13 +11572,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11673,17 +11673,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
@@ -11721,7 +11721,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11803,14 +11803,14 @@
       <c r="P108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>0</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>0</v>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T108" s="10" t="n">
         <v>1</v>
@@ -11818,11 +11818,11 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>0</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>5</v>
@@ -11875,13 +11875,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>e&amp; Toastmasters Club</t>
+          <t>etisalat Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11976,17 +11976,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="7" t="n">
@@ -12018,13 +12018,13 @@
         <v>1</v>
       </c>
       <c r="U110" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V110" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -12081,13 +12081,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -12291,13 +12291,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12483,7 +12483,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12553,8 +12553,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12640,11 +12640,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12798,13 +12798,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>14</v>
+        <v>-13</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12903,13 +12903,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12947,8 +12947,8 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>2</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -13008,13 +13008,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13109,13 +13109,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13210,13 +13210,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q122" s="10" t="n">
         <v>2</v>
@@ -13251,14 +13251,14 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>7</v>
@@ -13315,13 +13315,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>7</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13420,13 +13420,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -13455,14 +13455,14 @@
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S124" s="9" t="n">
-        <v>1</v>
+      <c r="S124" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U124" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V124" s="9" t="n">
         <v>2</v>
@@ -13521,13 +13521,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="8" t="inlineStr">
         <is>
@@ -13622,13 +13622,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13727,17 +13727,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13832,13 +13832,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13876,8 +13876,8 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>3</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13937,13 +13937,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -14137,17 +14137,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="7" t="n">
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14242,13 +14242,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>7</v>
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14347,13 +14347,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" s="9" t="n">
         <v>0</v>
@@ -14391,8 +14391,8 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14448,13 +14448,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -14549,13 +14549,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>4</v>
       </c>
       <c r="W135" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -14654,13 +14654,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14759,13 +14759,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14806,8 +14806,8 @@
       <c r="V137" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W137" s="9" t="n">
-        <v>3</v>
+      <c r="W137" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14850,7 +14850,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14864,13 +14864,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14902,14 +14902,14 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="9" t="n">
-        <v>0</v>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>2</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14969,13 +14969,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
@@ -15070,13 +15070,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15171,17 +15171,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="7" t="n">
@@ -15276,13 +15276,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>3</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15377,13 +15377,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15478,13 +15478,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15522,11 +15522,11 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>3</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -15583,13 +15583,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -15789,13 +15789,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -16096,13 +16096,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16197,17 +16197,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16241,8 +16241,8 @@
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="9" t="n">
-        <v>3</v>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16298,13 +16298,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>0</v>
       </c>
       <c r="S153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" s="9" t="n">
         <v>0</v>
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16603,13 +16603,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -16708,17 +16708,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L156" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M156" s="7" t="n">
@@ -16809,17 +16809,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="7" t="n">
@@ -16914,17 +16914,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -17120,13 +17120,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
@@ -17225,13 +17225,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17330,13 +17330,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>4</v>
       </c>
       <c r="W162" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>7</v>
@@ -17431,13 +17431,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>4</v>
       </c>
       <c r="W163" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>7</v>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17532,13 +17532,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -17579,8 +17579,8 @@
       <c r="V164" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W164" s="9" t="n">
-        <v>2</v>
+      <c r="W164" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>7</v>
@@ -17637,17 +17637,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -17724,7 +17724,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17738,17 +17738,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="7" t="n">
@@ -17776,8 +17776,8 @@
       <c r="S166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T166" s="9" t="n">
-        <v>0</v>
+      <c r="T166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U166" s="9" t="n">
         <v>0</v>
@@ -17944,17 +17944,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L168" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="7" t="n">
@@ -17989,7 +17989,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -18049,13 +18049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18154,17 +18154,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L170" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M170" s="7" t="n">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
@@ -18297,8 +18297,8 @@
       <c r="U171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="9" t="n">
-        <v>1</v>
+      <c r="V171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18352,13 +18352,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18451,13 +18451,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L173" s="8" t="inlineStr">
         <is>
@@ -18550,17 +18550,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="7" t="n">
@@ -18598,7 +18598,7 @@
         <v>4</v>
       </c>
       <c r="W174" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X174" s="10" t="n">
         <v>7</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18649,13 +18649,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18696,8 +18696,8 @@
       <c r="V175" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W175" s="9" t="n">
-        <v>1</v>
+      <c r="W175" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>7</v>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18748,13 +18748,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
@@ -18792,8 +18792,8 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>3</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -18847,13 +18847,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L177" s="8" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18946,17 +18946,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L178" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M178" s="7" t="n">
@@ -18990,8 +18990,8 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>3</v>
+      <c r="V178" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -19144,17 +19144,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L180" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="7" t="n">
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q180" s="9" t="n">
         <v>0</v>
@@ -19189,7 +19189,7 @@
         <v>0</v>
       </c>
       <c r="V180" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19243,13 +19243,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19276,13 +19276,13 @@
         <v>2</v>
       </c>
       <c r="R181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S181" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T181" s="9" t="n">
-        <v>0</v>
+      <c r="T181" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U181" s="9" t="n">
         <v>0</v>
@@ -19291,7 +19291,7 @@
         <v>4</v>
       </c>
       <c r="W181" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>7</v>
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19371,8 +19371,8 @@
       <c r="P182" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" s="9" t="n">
-        <v>1</v>
+      <c r="Q182" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -19386,8 +19386,8 @@
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="9" t="n">
-        <v>2</v>
+      <c r="V182" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19427,7 +19427,7 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19468,10 +19468,10 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q183" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q183" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
@@ -19485,11 +19485,11 @@
       <c r="U183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V183" s="9" t="n">
-        <v>3</v>
+      <c r="V183" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W183" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X183" s="10" t="n">
         <v>7</v>
@@ -19738,13 +19738,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>0</v>
       </c>
       <c r="V186" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
@@ -19936,13 +19936,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L188" s="8" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -20035,13 +20035,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L189" s="8" t="inlineStr">
         <is>
@@ -20079,8 +20079,8 @@
       <c r="U189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V189" s="9" t="n">
-        <v>3</v>
+      <c r="V189" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
@@ -20134,13 +20134,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20233,17 +20233,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L191" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M191" s="7" t="n">
@@ -20277,11 +20277,11 @@
       <c r="U191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V191" s="9" t="n">
-        <v>0</v>
+      <c r="V191" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X191" s="10" t="n">
         <v>7</v>
@@ -20332,13 +20332,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -20431,17 +20431,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L193" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M193" s="7" t="n">
@@ -20629,13 +20629,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20728,13 +20728,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>1</v>
@@ -20766,8 +20766,8 @@
       <c r="S196" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T196" s="9" t="n">
-        <v>0</v>
+      <c r="T196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U196" s="9" t="n">
         <v>0</v>
@@ -20776,7 +20776,7 @@
         <v>4</v>
       </c>
       <c r="W196" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X196" s="10" t="n">
         <v>7</v>
@@ -20926,13 +20926,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L198" s="8" t="inlineStr">
         <is>
@@ -21025,13 +21025,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L199" s="8" t="inlineStr">
         <is>
@@ -21124,13 +21124,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L200" s="8" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21250,10 +21250,10 @@
         </is>
       </c>
       <c r="P201" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q201" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>0</v>
@@ -21322,13 +21322,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>4</v>
       </c>
       <c r="W202" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X202" s="10" t="n">
         <v>7</v>
@@ -21421,13 +21421,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
@@ -21520,13 +21520,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>4</v>
       </c>
       <c r="W204" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X204" s="10" t="n">
         <v>7</v>
@@ -21718,13 +21718,13 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L206" s="8" t="inlineStr">
         <is>
@@ -21817,17 +21817,17 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L207" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M207" s="7" t="n">
@@ -21862,7 +21862,7 @@
         <v>0</v>
       </c>
       <c r="V207" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W207" s="9" t="n">
         <v>0</v>
@@ -21985,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -22036,7 +22036,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -22102,13 +22102,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -22135,13 +22135,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22168,22 +22168,22 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -22201,7 +22201,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22216,7 +22216,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -22234,7 +22234,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22249,7 +22249,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22267,7 +22267,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -22282,7 +22282,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -22300,7 +22300,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -22315,7 +22315,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -22333,13 +22333,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -22366,7 +22366,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22381,7 +22381,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -22399,7 +22399,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22432,7 +22432,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -22447,7 +22447,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -22465,7 +22465,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22480,7 +22480,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -22498,13 +22498,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -22513,7 +22513,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -22579,7 +22579,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -22663,13 +22663,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -22729,7 +22729,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -22762,13 +22762,13 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -22795,7 +22795,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22810,7 +22810,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -22828,13 +22828,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -22861,7 +22861,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -22894,7 +22894,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22927,7 +22927,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22942,7 +22942,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -22975,7 +22975,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -22993,7 +22993,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -23041,7 +23041,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -23059,7 +23059,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -23074,7 +23074,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -23092,7 +23092,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -23107,7 +23107,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -23125,7 +23125,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -23140,7 +23140,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -23158,7 +23158,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -23206,7 +23206,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -23224,7 +23224,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -23257,7 +23257,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -23305,7 +23305,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -897,8 +897,8 @@
       <c r="R2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="9" t="n">
-        <v>1</v>
+      <c r="S2" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>4</v>
       </c>
       <c r="W2" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X2" s="10" t="n">
         <v>7</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3261,8 +3261,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3662,7 +3662,7 @@
         <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>0</v>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>4</v>
       </c>
       <c r="W33" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>7</v>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5514,8 +5514,8 @@
       <c r="P47" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" s="9" t="n">
-        <v>1</v>
+      <c r="Q47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5523,11 +5523,11 @@
       <c r="S47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
+      <c r="T47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V47" s="9" t="n">
         <v>2</v>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6125,8 +6125,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P53" s="9" t="n">
-        <v>3</v>
+      <c r="P53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>7</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6555,8 +6555,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>1</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="10" t="n">
         <v>2</v>
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8823,8 +8823,8 @@
       <c r="S79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
@@ -8833,7 +8833,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8890,13 +8890,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>6</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9343,8 +9343,8 @@
       <c r="T84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
         <v>4</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9718,13 +9718,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>2</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9765,8 +9765,8 @@
       <c r="V88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W88" s="9" t="n">
-        <v>2</v>
+      <c r="W88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9823,13 +9823,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" s="10" t="n">
         <v>1</v>
@@ -10388,7 +10388,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>7</v>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10445,17 +10445,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -10489,11 +10489,11 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W95" s="9" t="n">
-        <v>0</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>7</v>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11404,8 +11404,8 @@
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q112" s="10" t="n">
         <v>2</v>
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12798,13 +12798,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -12846,7 +12846,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X118" s="9" t="n">
         <v>2</v>
@@ -13315,13 +13315,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>7</v>
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13870,8 +13870,8 @@
       <c r="S128" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -13937,13 +13937,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14549,13 +14549,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>4</v>
       </c>
       <c r="W135" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -14759,13 +14759,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14864,13 +14864,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>5</v>
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15516,8 +15516,8 @@
       <c r="S144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
@@ -15613,7 +15613,7 @@
         <v>0</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -16197,13 +16197,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L151" s="8" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>5</v>
@@ -17330,13 +17330,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>4</v>
       </c>
       <c r="W162" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>7</v>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18352,13 +18352,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18399,8 +18399,8 @@
       <c r="V172" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W172" s="9" t="n">
-        <v>1</v>
+      <c r="W172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>7</v>
@@ -18649,13 +18649,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>4</v>
       </c>
       <c r="W175" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>7</v>
@@ -18748,13 +18748,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
@@ -19243,13 +19243,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>4</v>
       </c>
       <c r="W181" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>7</v>
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19441,13 +19441,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>0</v>
       </c>
       <c r="S183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" s="10" t="n">
         <v>1</v>
@@ -19488,8 +19488,8 @@
       <c r="V183" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W183" s="9" t="n">
-        <v>2</v>
+      <c r="W183" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X183" s="10" t="n">
         <v>7</v>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -20172,8 +20172,8 @@
       <c r="S190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="9" t="n">
-        <v>0</v>
+      <c r="T190" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U190" s="9" t="n">
         <v>0</v>
@@ -20318,7 +20318,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20332,13 +20332,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -20376,8 +20376,8 @@
       <c r="U192" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V192" s="9" t="n">
-        <v>2</v>
+      <c r="V192" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
@@ -21970,7 +21970,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -22102,7 +22102,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -22234,7 +22234,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22300,7 +22300,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -22465,7 +22465,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22498,7 +22498,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -22531,7 +22531,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22597,7 +22597,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -22663,7 +22663,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -22795,7 +22795,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22894,7 +22894,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -23059,7 +23059,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -23158,13 +23158,13 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/127/inyear.xlsx
+++ b/docs/d/127/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>6</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2827,14 +2827,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>3</v>
+      <c r="P21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="10" t="n">
         <v>2</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="W28" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>7</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4609,8 +4609,8 @@
       <c r="V38" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>3</v>
+      <c r="W38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5118,8 +5118,8 @@
       <c r="T43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
+      <c r="U43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V43" s="9" t="n">
         <v>0</v>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6752,8 +6752,8 @@
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="9" t="n">
-        <v>1</v>
+      <c r="S59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T59" s="10" t="n">
         <v>1</v>
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -11572,13 +11572,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11875,13 +11875,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11931,8 +11931,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12212,8 +12212,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P112" s="9" t="n">
-        <v>3</v>
+      <c r="P112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q112" s="10" t="n">
         <v>2</v>
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12798,13 +12798,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X118" s="9" t="n">
         <v>2</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>1</v>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13622,13 +13622,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13657,8 +13657,8 @@
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="9" t="n">
-        <v>1</v>
+      <c r="S126" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T126" s="10" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>7</v>
@@ -14640,7 +14640,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14683,14 +14683,14 @@
       <c r="P136" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" s="9" t="n">
-        <v>1</v>
+      <c r="Q136" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S136" s="9" t="n">
-        <v>1</v>
+      <c r="S136" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T136" s="9" t="n">
         <v>0</v>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14969,13 +14969,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15025,8 +15025,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15478,13 +15478,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -16399,13 +16399,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16603,13 +16603,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -16708,13 +16708,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -18385,7 +18385,7 @@
         <v>2</v>
       </c>
       <c r="R172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S172" s="9" t="n">
         <v>1</v>
@@ -18394,7 +18394,7 @@
         <v>1</v>
       </c>
       <c r="U172" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V172" s="10" t="n">
         <v>4</v>
@@ -18649,13 +18649,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>4</v>
       </c>
       <c r="W175" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>7</v>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19144,13 +19144,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L180" s="8" t="inlineStr">
         <is>
@@ -19188,8 +19188,8 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="9" t="n">
-        <v>3</v>
+      <c r="V180" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19279,13 +19279,13 @@
         <v>1</v>
       </c>
       <c r="S181" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U181" s="9" t="n">
-        <v>0</v>
+      <c r="U181" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V181" s="10" t="n">
         <v>4</v>
@@ -19375,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="R182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S182" s="9" t="n">
         <v>0</v>
@@ -19526,7 +19526,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19584,11 +19584,11 @@
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="9" t="n">
-        <v>0</v>
+      <c r="V184" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X184" s="9" t="n">
         <v>0</v>
@@ -20233,13 +20233,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L191" s="8" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>4</v>
       </c>
       <c r="W191" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X191" s="10" t="n">
         <v>7</v>
@@ -20362,7 +20362,7 @@
         <v>1</v>
       </c>
       <c r="Q192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R192" s="9" t="n">
         <v>0</v>
@@ -22069,7 +22069,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -22201,7 +22201,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22333,7 +22333,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -22696,7 +22696,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -22795,7 +22795,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22828,13 +22828,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -22861,7 +22861,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -23125,7 +23125,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -23158,7 +23158,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
